--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>250</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>20/09 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>19/09 16:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>20/09 14:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>175</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>175</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>150</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>140</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>140</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>140</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>19/09 16:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>140</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>140</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>140</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>140</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>140</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>125</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,97 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45919.06917210254</v>
+        <v>45919.06917210648</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | ERC Ingols</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ERC Ingolstadt – Grizzlys WolfsburgDEL (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+166%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45919.12642123525</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Poprad – K</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Poprad – KosiceSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45919.12642123525</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>175</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45919.12642123525</v>
+        <v>45919.12642123843</v>
       </c>
     </row>
     <row r="28">
@@ -1625,23 +1623,201 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>140</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45919.12642123843</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – HC Twk Innsbruck Die HaieICE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20/09 15:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+198%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45919.18431546541</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zvolen – S</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Zvolen – Slovan BratislavaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+182%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45919.18431546541</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KooKoo – S</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KooKoo – Sport VaasaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19/09 15:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45919.18431546541</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lukko – HP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lukko – HPKFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19/09 15:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>+107%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>45919.12642123525</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+98,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45919.18431546541</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>20/09 15:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>200</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45919.18431546541</v>
+        <v>45919.18431546296</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>200</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45919.18431546541</v>
+        <v>45919.18431546296</v>
       </c>
     </row>
     <row r="31">
@@ -1756,10 +1752,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>175</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1772,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45919.18431546541</v>
+        <v>45919.18431546296</v>
       </c>
     </row>
     <row r="32">
@@ -1801,23 +1795,156 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>140</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+98,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45919.18431546296</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Pioneers V</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pioneers Vorarlberg – BolzanoICE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+211%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45919.22218139387</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Tappara Ta</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tappara Tampere – KalPaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19/09 16:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45919.22218139387</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – MSHK ZilinaExtraliga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19/09 15:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>+98,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>45919.18431546541</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45919.22218139387</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>200</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45919.22218139387</v>
+        <v>45919.22218138889</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>19/09 16:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>150</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45919.22218139387</v>
+        <v>45919.22218138889</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,97 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45919.22218139387</v>
+        <v>45919.22218138889</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – Eisbären BerlinAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45919.27220572162</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ambri Piot</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ambri Piotta – ZSC LionsSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/09 17:45</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+92,7%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45919.27220572162</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -1967,10 +1967,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>150</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45919.27220572162</v>
+        <v>45919.27220571759</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>125</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45919.27220572162</v>
+        <v>45919.27220571759</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2027,6 +2027,96 @@
         <v>45919.27220571759</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Presov </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HC Presov – Dukla TrencinExtraliga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+126%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45919.35276971486</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaxjo Lake</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Vaxjo Lakers – Djurgaardens IFSHL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20/09 16:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+93,2%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45919.35276971486</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>150</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45919.35276971486</v>
+        <v>45919.35276971065</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>20/09 16:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>125</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,277 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45919.35276971486</v>
+        <v>45919.35276971065</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | FTC-Teleko</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FTC-Telekom – KACAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/09 16:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45919.39087199147</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – EC Villacher SVICE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/09 17:15</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+163%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45919.39087199147</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ajoie – Be</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ajoie – BernSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+135%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45919.39087199147</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Lausanne – Kloten FlyersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+134%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45919.39087199147</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zug – Rapp</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Zug – Rapperswil Jona LakersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+127%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45919.39087199147</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Davos – Lu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Davos – LuganoSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45919.39087199147</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>19/09 16:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45919.39087199147</v>
+        <v>45919.39087199074</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>175</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45919.39087199147</v>
+        <v>45919.39087199074</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>150</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45919.39087199147</v>
+        <v>45919.39087199074</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>150</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45919.39087199147</v>
+        <v>45919.39087199074</v>
       </c>
     </row>
     <row r="44">
@@ -2319,10 +2311,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>150</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2335,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45919.39087199147</v>
+        <v>45919.39087199074</v>
       </c>
     </row>
     <row r="45">
@@ -2364,10 +2354,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>140</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2380,7 +2368,142 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45919.39087199147</v>
+        <v>45919.39087199074</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Munich – A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Munich – Augsburger PantherAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+133%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45919.43224812249</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Iserlohn –</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Iserlohn – Nuremberg Ice TigersDEL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45919.43224812249</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – MichalovceSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19/09 15:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45919.43224812249</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>175</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45919.43224812249</v>
+        <v>45919.432248125</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>150</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45919.43224812249</v>
+        <v>45919.432248125</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>150</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,97 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45919.43224812249</v>
+        <v>45919.432248125</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ajoie P</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HC Ajoie Porrentruy – SC BernNational League A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45919.47072620496</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SC Rappers</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SC Rapperswil-Jona Lakers – LausanneNational League A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19/09 17:45</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+96,6%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45919.47072620496</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>140</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45919.47072620496</v>
+        <v>45919.4707262037</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>125</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,232 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45919.47072620496</v>
+        <v>45919.4707262037</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Spusu Vien</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spusu Vienna Capitals – Black Wings LinzICE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19/09 17:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+207%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45919.52967371198</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mountfield HK – Kometa BrnoRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+130%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45919.52967371198</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Plzen – Pa</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Plzen – PardubiceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45919.52967371198</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EV Zug – S</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EV Zug – SC Rapperswil-Jona LakersNational League A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45919.52967371198</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liberec – </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Liberec – KladnoRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/09 15:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45919.52967371198</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -2612,10 +2612,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>200</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45919.52967371198</v>
+        <v>45919.52967371527</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>150</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45919.52967371198</v>
+        <v>45919.52967371527</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>140</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45919.52967371198</v>
+        <v>45919.52967371527</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>140</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45919.52967371198</v>
+        <v>45919.52967371527</v>
       </c>
     </row>
     <row r="55">
@@ -2792,10 +2784,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>140</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2808,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45919.52967371198</v>
+        <v>45919.52967371527</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,51 @@
         <v>45919.52967371527</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nitra – Li</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nitra – Liptovsky MikulasSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+136%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45919.59756816293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>175</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45919.59756816293</v>
+        <v>45919.59756815972</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HIFK Helsi</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HIFK Helsinki – SaiPaLiiga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20/09 14:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45919.6398435368</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mountfield HK – HC Kometa BrnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+104%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45919.6398435368</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>20/09 14:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>150</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45919.6398435368</v>
+        <v>45919.63984354166</v>
       </c>
     </row>
     <row r="58">
@@ -2915,23 +2913,246 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>140</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+104%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45919.63984354166</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lausanne – EHC KlotenNational League A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>+104%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>45919.6398435368</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+121%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45919.68425921268</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Timrå IK –</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Timrå IK – Färjestad BKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20/09 13:15</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+81,2%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45919.68425921268</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Plzen –</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HC Plzen – HC PardubiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+80,6%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45919.68425921268</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Brynäs IF </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brynäs IF – Örebro HKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20/09 16:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+79,3%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45919.68425921268</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Växjö Lake</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Växjö Lakers HC – Djurgårdens IFSuède - Suède SHL A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20/09 16:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+76,8%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45919.68425921268</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>140</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45919.68425921268</v>
+        <v>45919.68425921296</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>20/09 13:15</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>125</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45919.68425921268</v>
+        <v>45919.68425921296</v>
       </c>
     </row>
     <row r="61">
@@ -3046,10 +3042,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>125</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3062,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45919.68425921268</v>
+        <v>45919.68425921296</v>
       </c>
     </row>
     <row r="62">
@@ -3091,10 +3085,8 @@
           <t>20/09 16:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>125</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3107,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45919.68425921268</v>
+        <v>45919.68425921296</v>
       </c>
     </row>
     <row r="63">
@@ -3136,23 +3128,381 @@
           <t>20/09 16:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>125</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+76,8%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45919.68425921296</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Jukurit – </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jukurit – KooKooFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20/09 14:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+99,1%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Schwenning</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Schwenninger Wild Wings – Kölner HaieAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+95,9%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Lugano </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HC Lugano – HC Ajoie PorrentruyNational League A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19/09 17:45</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>+76,8%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>45919.68425921268</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+91,7%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Frölunda HC – Luleå HFSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20/09 16:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+83,3%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – HC Rytiri KladnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>21/09 15:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+78,2%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Straubing TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+74,1%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Malmo Redh</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Malmo Redhawks – HV 71SHL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>20/09 16:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+69,9%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45919.72079697868</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cerro Port</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cerro Porteno – Sportivo AmelianoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20/09 22:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+68,7%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45919.72079697868</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>20/09 14:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>150</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="65">
@@ -3216,10 +3214,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>140</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3232,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="66">
@@ -3261,10 +3257,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>125</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3277,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="67">
@@ -3306,10 +3300,8 @@
           <t>20/09 16:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>125</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3322,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="68">
@@ -3351,10 +3343,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>125</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3367,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="69">
@@ -3396,10 +3386,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>125</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3412,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="70">
@@ -3441,10 +3429,8 @@
           <t>20/09 16:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>110</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3457,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45919.72079697868</v>
+        <v>45919.72079697916</v>
       </c>
     </row>
     <row r="71">
@@ -3486,23 +3472,426 @@
           <t>20/09 22:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>60</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+68,7%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45919.72079697916</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Genève-ServetteSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+95,9%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Kolos Kova</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Kolos Kovalivka – Veres RivneUPL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20/09 12:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>+68,7%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>45919.72079697868</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+72,7%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fribourg G</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fribourg Gotteron – Langnau TigersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+69,9%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Beitar Jer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem – Ironi Kiryat ShmonaPremier League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>20/09 17:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+69,4%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Linkopings</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Linkopings – Skelleftea AIKSHL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>20/09 13:15</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+66,7%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – TrinecRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>21/09 15:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+66,3%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ludogorets Razgrad – PFC MontanaBulgarie. Bulgarie - Parva Liga</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>28/09 17:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+63,0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | TPS – KalP</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TPS – KalPaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>20/09 14:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+56,3%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45919.77031183321</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | EHC Biel-B</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EHC Biel-Bienne – Ambri PiottaSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+54,0%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45919.77031183321</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>125</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>20/09 12:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>60</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>110</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="75">
@@ -3650,10 +3644,8 @@
           <t>20/09 17:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>60</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3666,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="76">
@@ -3695,10 +3687,8 @@
           <t>20/09 13:15</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>110</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3711,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="77">
@@ -3740,10 +3730,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>110</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3756,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="78">
@@ -3785,10 +3773,8 @@
           <t>28/09 17:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>60</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3801,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="79">
@@ -3830,10 +3816,8 @@
           <t>20/09 14:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>110</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3846,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
       </c>
     </row>
     <row r="80">
@@ -3875,10 +3859,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>98</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3891,7 +3873,187 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45919.77031183321</v>
+        <v>45919.7703118287</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | EC VSV – H</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EC VSV – HC PustertalAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>21/09 15:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+231%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45919.80324698464</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Jukurit Mi</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jukurit Mikkeli – KooKooLiiga</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>20/09 14:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45919.80324698464</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>20/09 17:45</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+73,7%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45919.80324698464</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lowen Fran</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Lowen Frankfurt – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+73,6%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45919.80324698464</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,10 +3902,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>225</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3918,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45919.80324698464</v>
+        <v>45919.80324697917</v>
       </c>
     </row>
     <row r="82">
@@ -3947,10 +3945,8 @@
           <t>20/09 14:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>150</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3963,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45919.80324698464</v>
+        <v>45919.80324697917</v>
       </c>
     </row>
     <row r="83">
@@ -3992,10 +3988,8 @@
           <t>20/09 17:45</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>110</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4008,7 +4002,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45919.80324698464</v>
+        <v>45919.80324697917</v>
       </c>
     </row>
     <row r="84">
@@ -4037,10 +4031,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>125</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4053,7 +4045,277 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45919.80324698464</v>
+        <v>45919.80324697917</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liptovsky </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas – ZvolenSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>21/09 15:00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45919.84886216007</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Michalovce</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Michalovce – NitraSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45919.84886216007</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Trencin – </t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Trencin – Banska BystricaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>21/09 12:30</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45919.84886216007</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zilina – P</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Zilina – PopradSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>21/09 15:30</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45919.84886216007</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kosice – S</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Kosice – Spisska Nova VesSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+97,8%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45919.84886216007</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Löwen Fran</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Löwen Frankfurt – Schwenninger Wild WingsAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>+95,7%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45919.84886216007</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4074,10 +4074,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F85" t="n">
+        <v>200</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4090,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45919.84886216007</v>
+        <v>45919.84886216435</v>
       </c>
     </row>
     <row r="86">
@@ -4119,10 +4117,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F86" t="n">
+        <v>175</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4135,7 +4131,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45919.84886216007</v>
+        <v>45919.84886216435</v>
       </c>
     </row>
     <row r="87">
@@ -4164,10 +4160,8 @@
           <t>21/09 12:30</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F87" t="n">
+        <v>150</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4180,7 +4174,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45919.84886216007</v>
+        <v>45919.84886216435</v>
       </c>
     </row>
     <row r="88">
@@ -4209,10 +4203,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F88" t="n">
+        <v>150</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4225,7 +4217,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45919.84886216007</v>
+        <v>45919.84886216435</v>
       </c>
     </row>
     <row r="89">
@@ -4254,10 +4246,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F89" t="n">
+        <v>140</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4270,7 +4260,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45919.84886216007</v>
+        <v>45919.84886216435</v>
       </c>
     </row>
     <row r="90">
@@ -4299,10 +4289,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F90" t="n">
+        <v>140</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4315,7 +4303,142 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45919.84886216007</v>
+        <v>45919.84886216435</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – PresovSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45919.88743016479</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Mich</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dukla Michalovce – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>45919.88743016479</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Malmö Redh</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Malmö Redhawks – HV71Suède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>20/09 16:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>+82,4%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>45919.88743016479</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4332,10 +4332,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F91" t="n">
+        <v>200</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4348,7 +4346,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45919.88743016479</v>
+        <v>45919.88743016204</v>
       </c>
     </row>
     <row r="92">
@@ -4377,10 +4375,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F92" t="n">
+        <v>150</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4393,7 +4389,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45919.88743016479</v>
+        <v>45919.88743016204</v>
       </c>
     </row>
     <row r="93">
@@ -4422,23 +4418,111 @@
           <t>20/09 16:00</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="n">
+        <v>125</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>+82,4%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>45919.88743016204</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – HC PresovExtraliga</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>+139%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45919.92990920688</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Timra IK –</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Timra IK – Farjestads BKSHL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>20/09 13:15</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>+82,4%</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>45919.88743016479</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>+89,8%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>45919.92990920688</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-19.xlsx
+++ b/data/valuebets_database_2025-09-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4461,10 +4461,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F94" t="n">
+        <v>175</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4477,7 +4475,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45919.92990920688</v>
+        <v>45919.92990920139</v>
       </c>
     </row>
     <row r="95">
@@ -4506,10 +4504,8 @@
           <t>20/09 13:15</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F95" t="n">
+        <v>125</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4522,7 +4518,142 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45919.92990920688</v>
+        <v>45919.92990920139</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nurnberg I</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Nurnberg Ice Tigers – Kölner HaieAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>21/09 12:00</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>+150%</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>45919.97134200526</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Pioneers VorarlbergICE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>+144%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>45919.97134200526</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Augsburger</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Augsburger Panther – Iserlohn RoostersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>21/09 17:00</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>+103%</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>45919.97134200526</v>
       </c>
     </row>
   </sheetData>
